--- a/data/output/summary_BAT-20260621-072055_20260621.xlsx
+++ b/data/output/summary_BAT-20260621-072055_20260621.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-21 07:21:27</t>
+          <t>2026-06-21 07:37:43</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>沪A-10001</t>
+          <t>沪A-10002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -838,31 +838,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>中舱</t>
+          <t>后舱</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-20 09:00</t>
+          <t>2026-06-20 10:30</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>-18.3</v>
+        <v>-20.1</v>
       </c>
       <c r="F2" t="n">
-        <v>-17.4</v>
+        <v>-17</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>合格</t>
+          <t>严重超差</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-05 09:00</t>
+          <t>2026-05-10 08:30</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -870,19 +870,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>剩14天</t>
+          <t>逾期12天</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>连续偏高</t>
+          <t>严重超差+校准逾期</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>沪A-10002</t>
+          <t>沪A-10004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -897,26 +897,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-20 10:30</t>
+          <t>2026-06-20 14:00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="F3" t="n">
-        <v>-18.9</v>
+        <v>-19.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>临近超差</t>
+          <t>严重超差</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-10 08:30</t>
+          <t>2026-04-15 14:00</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -924,12 +924,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>逾期12天</t>
+          <t>逾期37天</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>连续偏高+校准逾期</t>
+          <t>严重超差+校准逾期</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>后舱</t>
+          <t>中舱</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -955,17 +955,17 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-20.1</v>
+        <v>-20</v>
       </c>
       <c r="F4" t="n">
-        <v>-17</v>
+        <v>-18.9</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>严重超差</t>
+          <t>临近超差</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>严重超差+校准逾期</t>
+          <t>连续偏高+校准逾期</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>沪A-10004</t>
+          <t>沪A-10006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1059,26 +1059,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-20 14:00</t>
+          <t>2026-06-20 16:00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>-22</v>
+        <v>-19</v>
       </c>
       <c r="F6" t="n">
-        <v>-19.8</v>
+        <v>-17.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>严重超差</t>
+          <t>临近超差</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-04-15 14:00</t>
+          <t>2026-06-01 10:00</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1086,19 +1086,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>逾期37天</t>
+          <t>剩10天</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>严重超差+校准逾期</t>
+          <t>连续偏高</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>沪A-10006</t>
+          <t>沪A-10001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1113,26 +1113,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-20 16:00</t>
+          <t>2026-06-20 09:00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>-19</v>
+        <v>-18.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-17.2</v>
+        <v>-17.4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>临近超差</t>
+          <t>合格</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-06-01 10:00</t>
+          <t>2026-06-05 09:00</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>剩10天</t>
+          <t>剩14天</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
